--- a/SWTest/Outputs/Finalists/Navigator_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/Navigator_Analysis_Final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4521F943-CEA6-44B8-A0A8-48DEBB505E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B715BA95-B4D4-4A3D-8010-6AE434F79893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="310">
   <si>
     <t>SPN</t>
   </si>
@@ -955,6 +955,9 @@
   </si>
   <si>
     <t>Intake Air Heater Current Draw</t>
+  </si>
+  <si>
+    <t>Unit of Measurement</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1330,15 +1333,16 @@
     <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="61.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="70" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="62.28515625" customWidth="1"/>
-    <col min="14" max="14" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="10" max="10" width="70" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.28515625" customWidth="1"/>
+    <col min="15" max="15" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1364,25 +1368,28 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1407,9 +1414,6 @@
       <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
@@ -1417,10 +1421,13 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1445,23 +1452,23 @@
       <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
       <c r="K3" t="s">
         <v>19</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="N3" t="s">
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1486,9 +1493,6 @@
       <c r="H4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
       <c r="K4" t="s">
         <v>19</v>
       </c>
@@ -1496,10 +1500,13 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1524,20 +1531,20 @@
       <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>5</v>
       </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
       <c r="K5" t="s">
         <v>19</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1562,12 +1569,9 @@
       <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
       <c r="K6" t="s">
         <v>19</v>
       </c>
@@ -1575,10 +1579,13 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1603,12 +1610,9 @@
       <c r="H7" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
       <c r="K7" t="s">
         <v>19</v>
       </c>
@@ -1616,10 +1620,13 @@
         <v>19</v>
       </c>
       <c r="M7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1644,12 +1651,9 @@
       <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
       <c r="K8" t="s">
         <v>19</v>
       </c>
@@ -1657,10 +1661,13 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1685,23 +1692,23 @@
       <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
       <c r="K9" t="s">
         <v>19</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
-      <c r="N9" t="s">
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1726,12 +1733,9 @@
       <c r="H10" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
       <c r="K10" t="s">
         <v>19</v>
       </c>
@@ -1739,10 +1743,13 @@
         <v>19</v>
       </c>
       <c r="M10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1767,12 +1774,9 @@
       <c r="H11" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
       <c r="K11" t="s">
         <v>19</v>
       </c>
@@ -1780,10 +1784,13 @@
         <v>19</v>
       </c>
       <c r="M11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1808,12 +1815,9 @@
       <c r="H12" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J12" t="s">
-        <v>19</v>
-      </c>
       <c r="K12" t="s">
         <v>19</v>
       </c>
@@ -1821,10 +1825,13 @@
         <v>19</v>
       </c>
       <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -1849,12 +1856,9 @@
       <c r="H13" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J13" t="s">
-        <v>19</v>
-      </c>
       <c r="K13" t="s">
         <v>19</v>
       </c>
@@ -1862,10 +1866,13 @@
         <v>19</v>
       </c>
       <c r="M13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -1890,20 +1897,20 @@
       <c r="H14" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J14" t="s">
-        <v>19</v>
-      </c>
       <c r="K14" t="s">
         <v>19</v>
       </c>
       <c r="L14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -1928,23 +1935,23 @@
       <c r="H15" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>59</v>
       </c>
-      <c r="K15" t="s">
-        <v>19</v>
-      </c>
       <c r="L15" t="s">
         <v>19</v>
       </c>
       <c r="M15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1969,20 +1976,20 @@
       <c r="H16" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J16" t="s">
-        <v>19</v>
-      </c>
       <c r="K16" t="s">
         <v>19</v>
       </c>
       <c r="L16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -2007,23 +2014,23 @@
       <c r="H17" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <v>108</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>59</v>
       </c>
-      <c r="K17" t="s">
-        <v>19</v>
-      </c>
       <c r="L17" t="s">
         <v>19</v>
       </c>
       <c r="M17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -2048,12 +2055,9 @@
       <c r="H18" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J18" t="s">
-        <v>19</v>
-      </c>
       <c r="K18" t="s">
         <v>19</v>
       </c>
@@ -2061,13 +2065,16 @@
         <v>19</v>
       </c>
       <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" t="s">
         <v>72</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -2092,20 +2099,20 @@
       <c r="H19" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J19" t="s">
-        <v>19</v>
-      </c>
       <c r="K19" t="s">
         <v>19</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -2130,23 +2137,23 @@
       <c r="H20" t="s">
         <v>23</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>59</v>
       </c>
-      <c r="K20" t="s">
-        <v>19</v>
-      </c>
       <c r="L20" t="s">
         <v>19</v>
       </c>
       <c r="M20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" t="s">
         <v>79</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -2171,17 +2178,17 @@
       <c r="H21" t="s">
         <v>58</v>
       </c>
-      <c r="J21" t="s">
-        <v>19</v>
-      </c>
       <c r="K21" t="s">
         <v>19</v>
       </c>
       <c r="L21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -2206,12 +2213,9 @@
       <c r="H22" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J22" t="s">
-        <v>19</v>
-      </c>
       <c r="K22" t="s">
         <v>19</v>
       </c>
@@ -2219,13 +2223,16 @@
         <v>19</v>
       </c>
       <c r="M22" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" t="s">
         <v>85</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -2250,23 +2257,23 @@
       <c r="H23" t="s">
         <v>58</v>
       </c>
-      <c r="I23" s="2">
+      <c r="J23" s="2">
         <v>159</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>59</v>
       </c>
-      <c r="K23" t="s">
-        <v>19</v>
-      </c>
       <c r="L23" t="s">
         <v>19</v>
       </c>
       <c r="M23" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -2291,12 +2298,9 @@
       <c r="H24" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J24" t="s">
-        <v>19</v>
-      </c>
       <c r="K24" t="s">
         <v>19</v>
       </c>
@@ -2304,13 +2308,16 @@
         <v>19</v>
       </c>
       <c r="M24" t="s">
+        <v>19</v>
+      </c>
+      <c r="N24" t="s">
         <v>85</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -2335,20 +2342,20 @@
       <c r="H25" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J25" t="s">
-        <v>19</v>
-      </c>
       <c r="K25" t="s">
         <v>19</v>
       </c>
       <c r="L25" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -2373,20 +2380,20 @@
       <c r="H26" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J26" t="s">
-        <v>19</v>
-      </c>
       <c r="K26" t="s">
         <v>19</v>
       </c>
       <c r="L26" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -2411,20 +2418,20 @@
       <c r="H27" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J27" t="s">
-        <v>19</v>
-      </c>
       <c r="K27" t="s">
         <v>19</v>
       </c>
       <c r="L27" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>100</v>
       </c>
@@ -2449,12 +2456,9 @@
       <c r="H28" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J28" t="s">
-        <v>19</v>
-      </c>
       <c r="K28" t="s">
         <v>19</v>
       </c>
@@ -2462,10 +2466,13 @@
         <v>19</v>
       </c>
       <c r="M28" t="s">
+        <v>19</v>
+      </c>
+      <c r="N28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>103</v>
       </c>
@@ -2490,23 +2497,23 @@
       <c r="H29" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J29" t="s">
-        <v>19</v>
-      </c>
       <c r="K29" t="s">
         <v>19</v>
       </c>
       <c r="L29" t="s">
         <v>19</v>
       </c>
-      <c r="N29" t="s">
+      <c r="M29" t="s">
+        <v>19</v>
+      </c>
+      <c r="O29" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>106</v>
       </c>
@@ -2531,20 +2538,20 @@
       <c r="H30" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="2">
+      <c r="J30" s="2">
         <v>4</v>
       </c>
-      <c r="J30" t="s">
-        <v>19</v>
-      </c>
       <c r="K30" t="s">
         <v>19</v>
       </c>
       <c r="L30" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -2569,20 +2576,20 @@
       <c r="H31" t="s">
         <v>23</v>
       </c>
-      <c r="J31" t="s">
-        <v>19</v>
-      </c>
       <c r="K31" t="s">
         <v>19</v>
       </c>
       <c r="L31" t="s">
         <v>19</v>
       </c>
-      <c r="N31" t="s">
+      <c r="M31" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>110</v>
       </c>
@@ -2607,23 +2614,23 @@
       <c r="H32" t="s">
         <v>23</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>59</v>
       </c>
-      <c r="K32" t="s">
-        <v>19</v>
-      </c>
       <c r="L32" t="s">
         <v>19</v>
       </c>
       <c r="M32" t="s">
+        <v>19</v>
+      </c>
+      <c r="N32" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>112</v>
       </c>
@@ -2648,20 +2655,20 @@
       <c r="H33" t="s">
         <v>23</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>59</v>
       </c>
-      <c r="K33" t="s">
-        <v>19</v>
-      </c>
       <c r="L33" t="s">
         <v>19</v>
       </c>
       <c r="M33" t="s">
+        <v>19</v>
+      </c>
+      <c r="N33" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -2686,23 +2693,23 @@
       <c r="H34" t="s">
         <v>23</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="J34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>59</v>
       </c>
-      <c r="K34" t="s">
-        <v>19</v>
-      </c>
       <c r="L34" t="s">
         <v>19</v>
       </c>
       <c r="M34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N34" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2727,23 +2734,23 @@
       <c r="H35" t="s">
         <v>18</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>59</v>
       </c>
-      <c r="K35" t="s">
-        <v>19</v>
-      </c>
       <c r="L35" t="s">
         <v>19</v>
       </c>
       <c r="M35" t="s">
+        <v>19</v>
+      </c>
+      <c r="N35" t="s">
         <v>121</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -2768,23 +2775,23 @@
       <c r="H36" t="s">
         <v>18</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>59</v>
       </c>
-      <c r="K36" t="s">
-        <v>19</v>
-      </c>
       <c r="L36" t="s">
         <v>19</v>
       </c>
       <c r="M36" t="s">
+        <v>19</v>
+      </c>
+      <c r="N36" t="s">
         <v>90</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -2809,23 +2816,23 @@
       <c r="H37" t="s">
         <v>18</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>59</v>
       </c>
-      <c r="K37" t="s">
-        <v>19</v>
-      </c>
       <c r="L37" t="s">
         <v>19</v>
       </c>
       <c r="M37" t="s">
+        <v>19</v>
+      </c>
+      <c r="N37" t="s">
         <v>90</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -2850,23 +2857,23 @@
       <c r="H38" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>108</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>59</v>
       </c>
-      <c r="K38" t="s">
-        <v>19</v>
-      </c>
       <c r="L38" t="s">
         <v>19</v>
       </c>
       <c r="M38" t="s">
+        <v>19</v>
+      </c>
+      <c r="N38" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>130</v>
       </c>
@@ -2891,23 +2898,23 @@
       <c r="H39" t="s">
         <v>18</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>59</v>
       </c>
-      <c r="K39" t="s">
-        <v>19</v>
-      </c>
       <c r="L39" t="s">
         <v>19</v>
       </c>
       <c r="M39" t="s">
+        <v>19</v>
+      </c>
+      <c r="N39" t="s">
         <v>90</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -2932,23 +2939,23 @@
       <c r="H40" t="s">
         <v>18</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>59</v>
       </c>
-      <c r="K40" t="s">
-        <v>19</v>
-      </c>
       <c r="L40" t="s">
         <v>19</v>
       </c>
       <c r="M40" t="s">
+        <v>19</v>
+      </c>
+      <c r="N40" t="s">
         <v>90</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>135</v>
       </c>
@@ -2973,23 +2980,23 @@
       <c r="H41" t="s">
         <v>18</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="2">
         <v>66</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>59</v>
       </c>
-      <c r="K41" t="s">
-        <v>19</v>
-      </c>
       <c r="L41" t="s">
         <v>19</v>
       </c>
       <c r="M41" t="s">
+        <v>19</v>
+      </c>
+      <c r="N41" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3014,23 +3021,23 @@
       <c r="H42" t="s">
         <v>58</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>59</v>
       </c>
-      <c r="K42" t="s">
-        <v>19</v>
-      </c>
       <c r="L42" t="s">
         <v>19</v>
       </c>
       <c r="M42" t="s">
+        <v>19</v>
+      </c>
+      <c r="N42" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -3055,23 +3062,23 @@
       <c r="H43" t="s">
         <v>18</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>59</v>
       </c>
-      <c r="K43" t="s">
-        <v>19</v>
-      </c>
       <c r="L43" t="s">
         <v>19</v>
       </c>
       <c r="M43" t="s">
+        <v>19</v>
+      </c>
+      <c r="N43" t="s">
         <v>90</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>143</v>
       </c>
@@ -3096,20 +3103,20 @@
       <c r="H44" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="J44" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J44" t="s">
-        <v>19</v>
-      </c>
       <c r="K44" t="s">
         <v>19</v>
       </c>
       <c r="L44" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -3134,9 +3141,6 @@
       <c r="H45" t="s">
         <v>23</v>
       </c>
-      <c r="J45" t="s">
-        <v>19</v>
-      </c>
       <c r="K45" t="s">
         <v>19</v>
       </c>
@@ -3144,10 +3148,13 @@
         <v>19</v>
       </c>
       <c r="M45" t="s">
+        <v>19</v>
+      </c>
+      <c r="N45" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>149</v>
       </c>
@@ -3172,20 +3179,20 @@
       <c r="H46" t="s">
         <v>18</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="J46" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J46" t="s">
-        <v>19</v>
-      </c>
       <c r="K46" t="s">
         <v>19</v>
       </c>
       <c r="L46" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>152</v>
       </c>
@@ -3210,20 +3217,20 @@
       <c r="H47" t="s">
         <v>23</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="J47" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="J47" t="s">
-        <v>19</v>
-      </c>
       <c r="K47" t="s">
         <v>19</v>
       </c>
       <c r="L47" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>156</v>
       </c>
@@ -3248,12 +3255,9 @@
       <c r="H48" t="s">
         <v>23</v>
       </c>
-      <c r="I48" s="2">
+      <c r="J48" s="2">
         <v>7</v>
       </c>
-      <c r="J48" t="s">
-        <v>19</v>
-      </c>
       <c r="K48" t="s">
         <v>19</v>
       </c>
@@ -3261,10 +3265,13 @@
         <v>19</v>
       </c>
       <c r="M48" t="s">
+        <v>19</v>
+      </c>
+      <c r="N48" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>159</v>
       </c>
@@ -3289,23 +3296,23 @@
       <c r="H49" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="J49" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="J49" t="s">
-        <v>19</v>
-      </c>
       <c r="K49" t="s">
         <v>19</v>
       </c>
       <c r="L49" t="s">
         <v>19</v>
       </c>
-      <c r="N49" t="s">
+      <c r="M49" t="s">
+        <v>19</v>
+      </c>
+      <c r="O49" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>163</v>
       </c>
@@ -3330,23 +3337,23 @@
       <c r="H50" t="s">
         <v>58</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="J50" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>59</v>
       </c>
-      <c r="K50" t="s">
-        <v>19</v>
-      </c>
       <c r="L50" t="s">
         <v>19</v>
       </c>
       <c r="M50" t="s">
+        <v>19</v>
+      </c>
+      <c r="N50" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>165</v>
       </c>
@@ -3371,17 +3378,17 @@
       <c r="H51" t="s">
         <v>23</v>
       </c>
-      <c r="J51" t="s">
-        <v>19</v>
-      </c>
       <c r="K51" t="s">
         <v>19</v>
       </c>
       <c r="L51" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>167</v>
       </c>
@@ -3406,23 +3413,23 @@
       <c r="H52" t="s">
         <v>23</v>
       </c>
-      <c r="I52" s="2">
+      <c r="J52" s="2">
         <v>15</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>59</v>
       </c>
-      <c r="K52" t="s">
-        <v>19</v>
-      </c>
       <c r="L52" t="s">
         <v>19</v>
       </c>
       <c r="M52" t="s">
+        <v>19</v>
+      </c>
+      <c r="N52" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>169</v>
       </c>
@@ -3447,12 +3454,9 @@
       <c r="H53" t="s">
         <v>23</v>
       </c>
-      <c r="I53" s="2">
+      <c r="J53" s="2">
         <v>629</v>
       </c>
-      <c r="J53" t="s">
-        <v>19</v>
-      </c>
       <c r="K53" t="s">
         <v>19</v>
       </c>
@@ -3460,10 +3464,13 @@
         <v>19</v>
       </c>
       <c r="M53" t="s">
+        <v>19</v>
+      </c>
+      <c r="N53" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>172</v>
       </c>
@@ -3488,23 +3495,23 @@
       <c r="H54" t="s">
         <v>23</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="J54" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>59</v>
       </c>
-      <c r="K54" t="s">
-        <v>19</v>
-      </c>
       <c r="L54" t="s">
         <v>19</v>
       </c>
       <c r="M54" t="s">
+        <v>19</v>
+      </c>
+      <c r="N54" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>176</v>
       </c>
@@ -3529,23 +3536,23 @@
       <c r="H55" t="s">
         <v>58</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="J55" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>59</v>
       </c>
-      <c r="K55" t="s">
-        <v>19</v>
-      </c>
       <c r="L55" t="s">
         <v>19</v>
       </c>
       <c r="M55" t="s">
+        <v>19</v>
+      </c>
+      <c r="N55" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>179</v>
       </c>
@@ -3570,20 +3577,20 @@
       <c r="H56" t="s">
         <v>23</v>
       </c>
-      <c r="J56" t="s">
-        <v>19</v>
-      </c>
       <c r="K56" t="s">
         <v>19</v>
       </c>
       <c r="L56" t="s">
+        <v>19</v>
+      </c>
+      <c r="M56" t="s">
         <v>59</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -3608,26 +3615,26 @@
       <c r="H57" t="s">
         <v>23</v>
       </c>
-      <c r="I57" s="2" t="s">
+      <c r="J57" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="J57" t="s">
-        <v>19</v>
-      </c>
       <c r="K57" t="s">
         <v>19</v>
       </c>
       <c r="L57" t="s">
+        <v>19</v>
+      </c>
+      <c r="M57" t="s">
         <v>59</v>
       </c>
-      <c r="M57" t="s">
+      <c r="N57" t="s">
         <v>181</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -3652,23 +3659,23 @@
       <c r="H58" t="s">
         <v>58</v>
       </c>
-      <c r="I58" s="2" t="s">
+      <c r="J58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>59</v>
       </c>
-      <c r="K58" t="s">
-        <v>19</v>
-      </c>
       <c r="L58" t="s">
         <v>19</v>
       </c>
       <c r="M58" t="s">
+        <v>19</v>
+      </c>
+      <c r="N58" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>189</v>
       </c>
@@ -3693,26 +3700,26 @@
       <c r="H59" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="J59" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>59</v>
       </c>
-      <c r="K59" t="s">
-        <v>19</v>
-      </c>
       <c r="L59" t="s">
         <v>19</v>
       </c>
       <c r="M59" t="s">
+        <v>19</v>
+      </c>
+      <c r="N59" t="s">
         <v>192</v>
       </c>
-      <c r="N59" t="s">
+      <c r="O59" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>194</v>
       </c>
@@ -3737,12 +3744,9 @@
       <c r="H60" t="s">
         <v>23</v>
       </c>
-      <c r="I60" s="2" t="s">
+      <c r="J60" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="J60" t="s">
-        <v>19</v>
-      </c>
       <c r="K60" t="s">
         <v>19</v>
       </c>
@@ -3750,10 +3754,13 @@
         <v>19</v>
       </c>
       <c r="M60" t="s">
+        <v>19</v>
+      </c>
+      <c r="N60" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -3778,23 +3785,23 @@
       <c r="H61" t="s">
         <v>23</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>59</v>
       </c>
-      <c r="K61" t="s">
-        <v>19</v>
-      </c>
       <c r="L61" t="s">
         <v>19</v>
       </c>
       <c r="M61" t="s">
+        <v>19</v>
+      </c>
+      <c r="N61" t="s">
         <v>199</v>
       </c>
-      <c r="N61" t="s">
+      <c r="O61" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>201</v>
       </c>
@@ -3819,23 +3826,23 @@
       <c r="H62" t="s">
         <v>23</v>
       </c>
-      <c r="I62" s="2">
+      <c r="J62" s="2">
         <v>40</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>59</v>
       </c>
-      <c r="K62" t="s">
-        <v>19</v>
-      </c>
       <c r="L62" t="s">
         <v>19</v>
       </c>
       <c r="M62" t="s">
+        <v>19</v>
+      </c>
+      <c r="N62" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>205</v>
       </c>
@@ -3860,12 +3867,9 @@
       <c r="H63" t="s">
         <v>23</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J63" t="s">
-        <v>19</v>
-      </c>
       <c r="K63" t="s">
         <v>19</v>
       </c>
@@ -3873,13 +3877,16 @@
         <v>19</v>
       </c>
       <c r="M63" t="s">
+        <v>19</v>
+      </c>
+      <c r="N63" t="s">
         <v>85</v>
       </c>
-      <c r="N63" t="s">
+      <c r="O63" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>207</v>
       </c>
@@ -3904,20 +3911,20 @@
       <c r="H64" t="s">
         <v>23</v>
       </c>
-      <c r="I64" s="2" t="s">
+      <c r="J64" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="J64" t="s">
-        <v>19</v>
-      </c>
       <c r="K64" t="s">
         <v>19</v>
       </c>
       <c r="L64" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>210</v>
       </c>
@@ -3942,23 +3949,23 @@
       <c r="H65" t="s">
         <v>23</v>
       </c>
-      <c r="I65" s="2">
+      <c r="J65" s="2">
         <v>111</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>59</v>
       </c>
-      <c r="K65" t="s">
-        <v>19</v>
-      </c>
       <c r="L65" t="s">
         <v>19</v>
       </c>
       <c r="M65" t="s">
+        <v>19</v>
+      </c>
+      <c r="N65" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>213</v>
       </c>
@@ -3983,12 +3990,9 @@
       <c r="H66" t="s">
         <v>23</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="J66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J66" t="s">
-        <v>19</v>
-      </c>
       <c r="K66" t="s">
         <v>19</v>
       </c>
@@ -3996,13 +4000,16 @@
         <v>19</v>
       </c>
       <c r="M66" t="s">
+        <v>19</v>
+      </c>
+      <c r="N66" t="s">
         <v>85</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O66" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>215</v>
       </c>
@@ -4027,23 +4034,23 @@
       <c r="H67" t="s">
         <v>23</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="J67" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>59</v>
       </c>
-      <c r="K67" t="s">
-        <v>19</v>
-      </c>
       <c r="L67" t="s">
         <v>19</v>
       </c>
       <c r="M67" t="s">
+        <v>19</v>
+      </c>
+      <c r="N67" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>219</v>
       </c>
@@ -4068,20 +4075,20 @@
       <c r="H68" t="s">
         <v>23</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J68" t="s">
-        <v>19</v>
-      </c>
       <c r="K68" t="s">
         <v>19</v>
       </c>
       <c r="L68" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>221</v>
       </c>
@@ -4106,12 +4113,9 @@
       <c r="H69" t="s">
         <v>58</v>
       </c>
-      <c r="I69" s="2">
+      <c r="J69" s="2">
         <v>89</v>
       </c>
-      <c r="J69" t="s">
-        <v>19</v>
-      </c>
       <c r="K69" t="s">
         <v>19</v>
       </c>
@@ -4119,10 +4123,13 @@
         <v>19</v>
       </c>
       <c r="M69" t="s">
+        <v>19</v>
+      </c>
+      <c r="N69" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>224</v>
       </c>
@@ -4147,23 +4154,23 @@
       <c r="H70" t="s">
         <v>23</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="J70" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>59</v>
       </c>
-      <c r="K70" t="s">
-        <v>19</v>
-      </c>
       <c r="L70" t="s">
         <v>19</v>
       </c>
       <c r="M70" t="s">
+        <v>19</v>
+      </c>
+      <c r="N70" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>226</v>
       </c>
@@ -4188,23 +4195,23 @@
       <c r="H71" t="s">
         <v>23</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="J71" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="J71" t="s">
-        <v>19</v>
-      </c>
       <c r="K71" t="s">
         <v>19</v>
       </c>
       <c r="L71" t="s">
         <v>19</v>
       </c>
-      <c r="N71" t="s">
+      <c r="M71" t="s">
+        <v>19</v>
+      </c>
+      <c r="O71" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>229</v>
       </c>
@@ -4229,23 +4236,23 @@
       <c r="H72" t="s">
         <v>23</v>
       </c>
-      <c r="J72" t="s">
-        <v>19</v>
-      </c>
       <c r="K72" t="s">
         <v>19</v>
       </c>
       <c r="L72" t="s">
+        <v>19</v>
+      </c>
+      <c r="M72" t="s">
         <v>59</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>181</v>
       </c>
-      <c r="N72" t="s">
+      <c r="O72" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>231</v>
       </c>
@@ -4270,20 +4277,20 @@
       <c r="H73" t="s">
         <v>23</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="J73" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="J73" t="s">
-        <v>19</v>
-      </c>
       <c r="K73" t="s">
         <v>19</v>
       </c>
       <c r="L73" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>234</v>
       </c>
@@ -4308,26 +4315,26 @@
       <c r="H74" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="2" t="s">
+      <c r="J74" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="J74" t="s">
-        <v>19</v>
-      </c>
       <c r="K74" t="s">
         <v>19</v>
       </c>
       <c r="L74" t="s">
+        <v>19</v>
+      </c>
+      <c r="M74" t="s">
         <v>59</v>
       </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>181</v>
       </c>
-      <c r="N74" t="s">
+      <c r="O74" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>238</v>
       </c>
@@ -4352,20 +4359,20 @@
       <c r="H75" t="s">
         <v>18</v>
       </c>
-      <c r="I75" s="2" t="s">
+      <c r="J75" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J75" t="s">
-        <v>19</v>
-      </c>
       <c r="K75" t="s">
         <v>19</v>
       </c>
       <c r="L75" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>240</v>
       </c>
@@ -4390,9 +4397,6 @@
       <c r="H76" t="s">
         <v>18</v>
       </c>
-      <c r="J76" t="s">
-        <v>19</v>
-      </c>
       <c r="K76" t="s">
         <v>19</v>
       </c>
@@ -4400,10 +4404,13 @@
         <v>19</v>
       </c>
       <c r="M76" t="s">
+        <v>19</v>
+      </c>
+      <c r="N76" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>243</v>
       </c>
@@ -4428,20 +4435,20 @@
       <c r="H77" t="s">
         <v>18</v>
       </c>
-      <c r="J77" t="s">
-        <v>19</v>
-      </c>
       <c r="K77" t="s">
+        <v>19</v>
+      </c>
+      <c r="L77" t="s">
         <v>59</v>
       </c>
-      <c r="L77" t="s">
-        <v>19</v>
-      </c>
       <c r="M77" t="s">
+        <v>19</v>
+      </c>
+      <c r="N77" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>246</v>
       </c>
@@ -4466,20 +4473,20 @@
       <c r="H78" t="s">
         <v>18</v>
       </c>
-      <c r="I78" s="2">
+      <c r="J78" s="2">
         <v>3</v>
       </c>
-      <c r="J78" t="s">
-        <v>19</v>
-      </c>
       <c r="K78" t="s">
         <v>19</v>
       </c>
       <c r="L78" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>246</v>
       </c>
@@ -4504,20 +4511,20 @@
       <c r="H79" t="s">
         <v>23</v>
       </c>
-      <c r="J79" t="s">
-        <v>19</v>
-      </c>
       <c r="K79" t="s">
         <v>19</v>
       </c>
       <c r="L79" t="s">
         <v>19</v>
       </c>
-      <c r="N79" t="s">
+      <c r="M79" t="s">
+        <v>19</v>
+      </c>
+      <c r="O79" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>250</v>
       </c>
@@ -4542,23 +4549,23 @@
       <c r="H80" t="s">
         <v>58</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>159</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>59</v>
       </c>
-      <c r="K80" t="s">
-        <v>19</v>
-      </c>
       <c r="L80" t="s">
         <v>19</v>
       </c>
       <c r="M80" t="s">
+        <v>19</v>
+      </c>
+      <c r="N80" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>252</v>
       </c>
@@ -4583,12 +4590,9 @@
       <c r="H81" t="s">
         <v>58</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="J81" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J81" t="s">
-        <v>19</v>
-      </c>
       <c r="K81" t="s">
         <v>19</v>
       </c>
@@ -4596,10 +4600,13 @@
         <v>19</v>
       </c>
       <c r="M81" t="s">
+        <v>19</v>
+      </c>
+      <c r="N81" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>254</v>
       </c>
@@ -4624,12 +4631,9 @@
       <c r="H82" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="2">
+      <c r="J82" s="2">
         <v>159</v>
       </c>
-      <c r="J82" t="s">
-        <v>19</v>
-      </c>
       <c r="K82" t="s">
         <v>19</v>
       </c>
@@ -4637,10 +4641,13 @@
         <v>19</v>
       </c>
       <c r="M82" t="s">
+        <v>19</v>
+      </c>
+      <c r="N82" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>257</v>
       </c>
@@ -4665,12 +4672,9 @@
       <c r="H83" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="2">
+      <c r="J83" s="2">
         <v>159</v>
       </c>
-      <c r="J83" t="s">
-        <v>19</v>
-      </c>
       <c r="K83" t="s">
         <v>19</v>
       </c>
@@ -4678,10 +4682,13 @@
         <v>19</v>
       </c>
       <c r="M83" t="s">
+        <v>19</v>
+      </c>
+      <c r="N83" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>259</v>
       </c>
@@ -4706,12 +4713,9 @@
       <c r="H84" t="s">
         <v>23</v>
       </c>
-      <c r="I84" s="2">
+      <c r="J84" s="2">
         <v>159</v>
       </c>
-      <c r="J84" t="s">
-        <v>19</v>
-      </c>
       <c r="K84" t="s">
         <v>19</v>
       </c>
@@ -4719,10 +4723,13 @@
         <v>19</v>
       </c>
       <c r="M84" t="s">
+        <v>19</v>
+      </c>
+      <c r="N84" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>262</v>
       </c>
@@ -4747,12 +4754,9 @@
       <c r="H85" t="s">
         <v>23</v>
       </c>
-      <c r="I85" s="2">
+      <c r="J85" s="2">
         <v>159</v>
       </c>
-      <c r="J85" t="s">
-        <v>19</v>
-      </c>
       <c r="K85" t="s">
         <v>19</v>
       </c>
@@ -4760,10 +4764,13 @@
         <v>19</v>
       </c>
       <c r="M85" t="s">
+        <v>19</v>
+      </c>
+      <c r="N85" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>264</v>
       </c>
@@ -4788,20 +4795,20 @@
       <c r="H86" t="s">
         <v>23</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="J86" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J86" t="s">
-        <v>19</v>
-      </c>
       <c r="K86" t="s">
         <v>19</v>
       </c>
       <c r="L86" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>266</v>
       </c>
@@ -4826,20 +4833,20 @@
       <c r="H87" t="s">
         <v>23</v>
       </c>
-      <c r="I87" s="2">
+      <c r="J87" s="2">
         <v>33</v>
       </c>
-      <c r="J87" t="s">
-        <v>19</v>
-      </c>
       <c r="K87" t="s">
         <v>19</v>
       </c>
       <c r="L87" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>269</v>
       </c>
@@ -4864,26 +4871,26 @@
       <c r="H88" t="s">
         <v>18</v>
       </c>
-      <c r="I88" s="2">
+      <c r="J88" s="2">
         <v>49</v>
       </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="s">
-        <v>19</v>
+      <c r="K88" t="b">
+        <v>0</v>
       </c>
       <c r="L88" t="s">
         <v>19</v>
       </c>
       <c r="M88" t="s">
+        <v>19</v>
+      </c>
+      <c r="N88" t="s">
         <v>272</v>
       </c>
-      <c r="N88" t="s">
+      <c r="O88" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -4908,20 +4915,20 @@
       <c r="H89" t="s">
         <v>18</v>
       </c>
-      <c r="I89" s="2">
+      <c r="J89" s="2">
         <v>127</v>
       </c>
-      <c r="J89" t="s">
-        <v>19</v>
-      </c>
       <c r="K89" t="s">
         <v>19</v>
       </c>
       <c r="L89" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>276</v>
       </c>
@@ -4946,20 +4953,20 @@
       <c r="H90" t="s">
         <v>23</v>
       </c>
-      <c r="I90" s="2" t="s">
+      <c r="J90" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J90" t="s">
-        <v>19</v>
-      </c>
       <c r="K90" t="s">
         <v>19</v>
       </c>
       <c r="L90" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>278</v>
       </c>
@@ -4984,23 +4991,23 @@
       <c r="H91" t="s">
         <v>23</v>
       </c>
-      <c r="I91" s="2">
+      <c r="J91" s="2">
         <v>111</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>59</v>
       </c>
-      <c r="K91" t="s">
-        <v>19</v>
-      </c>
       <c r="L91" t="s">
         <v>19</v>
       </c>
       <c r="M91" t="s">
+        <v>19</v>
+      </c>
+      <c r="N91" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>281</v>
       </c>
@@ -5025,26 +5032,26 @@
       <c r="H92" t="s">
         <v>23</v>
       </c>
-      <c r="I92" s="2" t="s">
+      <c r="J92" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="J92" t="s">
-        <v>19</v>
-      </c>
       <c r="K92" t="s">
         <v>19</v>
       </c>
       <c r="L92" t="s">
+        <v>19</v>
+      </c>
+      <c r="M92" t="s">
         <v>59</v>
       </c>
-      <c r="M92" t="s">
+      <c r="N92" t="s">
         <v>181</v>
       </c>
-      <c r="N92" t="s">
+      <c r="O92" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>284</v>
       </c>
@@ -5069,20 +5076,20 @@
       <c r="H93" t="s">
         <v>23</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>59</v>
       </c>
-      <c r="K93" t="s">
-        <v>19</v>
-      </c>
       <c r="L93" t="s">
         <v>19</v>
       </c>
       <c r="M93" t="s">
+        <v>19</v>
+      </c>
+      <c r="N93" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>287</v>
       </c>
@@ -5107,12 +5114,9 @@
       <c r="H94" t="s">
         <v>23</v>
       </c>
-      <c r="I94" s="2" t="s">
+      <c r="J94" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="J94" t="s">
-        <v>19</v>
-      </c>
       <c r="K94" t="s">
         <v>19</v>
       </c>
@@ -5120,13 +5124,16 @@
         <v>19</v>
       </c>
       <c r="M94" t="s">
+        <v>19</v>
+      </c>
+      <c r="N94" t="s">
         <v>290</v>
       </c>
-      <c r="N94" t="s">
+      <c r="O94" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>292</v>
       </c>
@@ -5151,23 +5158,23 @@
       <c r="H95" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="2" t="s">
+      <c r="J95" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J95" t="s">
-        <v>19</v>
-      </c>
       <c r="K95" t="s">
         <v>19</v>
       </c>
       <c r="L95" t="s">
         <v>19</v>
       </c>
-      <c r="N95" t="s">
+      <c r="M95" t="s">
+        <v>19</v>
+      </c>
+      <c r="O95" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>295</v>
       </c>
@@ -5192,23 +5199,23 @@
       <c r="H96" t="s">
         <v>23</v>
       </c>
-      <c r="I96" s="2" t="s">
+      <c r="J96" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J96" t="s">
-        <v>19</v>
-      </c>
       <c r="K96" t="s">
         <v>19</v>
       </c>
       <c r="L96" t="s">
         <v>19</v>
       </c>
-      <c r="N96" t="s">
+      <c r="M96" t="s">
+        <v>19</v>
+      </c>
+      <c r="O96" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>297</v>
       </c>
@@ -5233,23 +5240,23 @@
       <c r="H97" t="s">
         <v>23</v>
       </c>
-      <c r="I97" s="2" t="s">
+      <c r="J97" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J97" t="s">
-        <v>19</v>
-      </c>
       <c r="K97" t="s">
         <v>19</v>
       </c>
       <c r="L97" t="s">
         <v>19</v>
       </c>
-      <c r="N97" t="s">
+      <c r="M97" t="s">
+        <v>19</v>
+      </c>
+      <c r="O97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>299</v>
       </c>
@@ -5274,12 +5281,9 @@
       <c r="H98" t="s">
         <v>23</v>
       </c>
-      <c r="I98" s="2">
+      <c r="J98" s="2">
         <v>52</v>
       </c>
-      <c r="J98" t="s">
-        <v>19</v>
-      </c>
       <c r="K98" t="s">
         <v>19</v>
       </c>
@@ -5287,13 +5291,16 @@
         <v>19</v>
       </c>
       <c r="M98" t="s">
+        <v>19</v>
+      </c>
+      <c r="N98" t="s">
         <v>301</v>
       </c>
-      <c r="N98" t="s">
+      <c r="O98" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>303</v>
       </c>
@@ -5318,12 +5325,9 @@
       <c r="H99" t="s">
         <v>23</v>
       </c>
-      <c r="I99" s="2">
+      <c r="J99" s="2">
         <v>45</v>
       </c>
-      <c r="J99" t="s">
-        <v>19</v>
-      </c>
       <c r="K99" t="s">
         <v>19</v>
       </c>
@@ -5331,13 +5335,16 @@
         <v>19</v>
       </c>
       <c r="M99" t="s">
+        <v>19</v>
+      </c>
+      <c r="N99" t="s">
         <v>301</v>
       </c>
-      <c r="N99" t="s">
+      <c r="O99" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>305</v>
       </c>
@@ -5362,12 +5369,9 @@
       <c r="H100" t="s">
         <v>23</v>
       </c>
-      <c r="I100" s="2">
+      <c r="J100" s="2">
         <v>40</v>
       </c>
-      <c r="J100" t="s">
-        <v>19</v>
-      </c>
       <c r="K100" t="s">
         <v>19</v>
       </c>
@@ -5375,13 +5379,16 @@
         <v>19</v>
       </c>
       <c r="M100" t="s">
+        <v>19</v>
+      </c>
+      <c r="N100" t="s">
         <v>301</v>
       </c>
-      <c r="N100" t="s">
+      <c r="O100" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>307</v>
       </c>
@@ -5406,12 +5413,9 @@
       <c r="H101" t="s">
         <v>23</v>
       </c>
-      <c r="I101" s="2">
+      <c r="J101" s="2">
         <v>15</v>
       </c>
-      <c r="J101" t="s">
-        <v>19</v>
-      </c>
       <c r="K101" t="s">
         <v>19</v>
       </c>
@@ -5419,9 +5423,12 @@
         <v>19</v>
       </c>
       <c r="M101" t="s">
+        <v>19</v>
+      </c>
+      <c r="N101" t="s">
         <v>301</v>
       </c>
-      <c r="N101" t="s">
+      <c r="O101" t="s">
         <v>302</v>
       </c>
     </row>

--- a/SWTest/Outputs/Finalists/Navigator_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/Navigator_Analysis_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227B5FAD-27DF-40CE-9EE8-E0DA8EE940E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5938E6-AD4A-47EE-8604-19D1A39099B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1185" windowWidth="26820" windowHeight="13755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="7140" windowWidth="28455" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
     <t>Dependency</t>
   </si>
   <si>
-    <t>Access Level (WinTrac)</t>
-  </si>
-  <si>
     <t>Event log when alarm code(s) set</t>
   </si>
   <si>
@@ -952,6 +949,9 @@
   </si>
   <si>
     <t>Unit of Measurement</t>
+  </si>
+  <si>
+    <t>Access Level (Wintrac)</t>
   </si>
 </sst>
 </file>
@@ -1345,8 +1345,8 @@
     <col min="11" max="11" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="190.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="209.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="109.42578125" customWidth="1"/>
+    <col min="15" max="15" width="116.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1372,39 +1372,39 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>0</v>
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="4"/>
@@ -1427,19 +1427,19 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>
@@ -1451,32 +1451,32 @@
         <v>0</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="b">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
@@ -1499,20 +1499,20 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D5" s="3" t="b">
         <v>1</v>
       </c>
@@ -1523,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="4">
@@ -1540,13 +1540,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3" t="b">
         <v>0</v>
@@ -1558,32 +1558,32 @@
         <v>0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3" t="b">
         <v>0</v>
@@ -1595,32 +1595,32 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="3" t="b">
         <v>0</v>
@@ -1632,32 +1632,32 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="b">
         <v>1</v>
@@ -1669,32 +1669,32 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="b">
         <v>0</v>
@@ -1706,32 +1706,32 @@
         <v>0</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="3" t="b">
         <v>0</v>
@@ -1743,32 +1743,32 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3" t="b">
         <v>0</v>
@@ -1780,32 +1780,32 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="b">
         <v>0</v>
@@ -1817,32 +1817,32 @@
         <v>0</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3" t="b">
         <v>1</v>
@@ -1854,14 +1854,14 @@
         <v>0</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1871,52 +1871,52 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="3" t="b">
         <v>1</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1945,91 +1945,91 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="H17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="4">
         <v>108</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="3" t="b">
         <v>1</v>
@@ -2041,14 +2041,14 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="b">
         <v>0</v>
@@ -2076,34 +2076,34 @@
         <v>0</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
       <c r="K20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="b">
         <v>1</v>
@@ -2115,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
@@ -2130,13 +2130,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3" t="b">
         <v>1</v>
@@ -2148,73 +2148,73 @@
         <v>0</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="4">
         <v>159</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="3" t="b">
         <v>1</v>
@@ -2226,34 +2226,34 @@
         <v>0</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="3" t="b">
         <v>1</v>
@@ -2265,14 +2265,14 @@
         <v>0</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
@@ -2282,13 +2282,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="3" t="b">
         <v>1</v>
@@ -2300,14 +2300,14 @@
         <v>0</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="3" t="b">
         <v>1</v>
@@ -2335,14 +2335,14 @@
         <v>0</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
@@ -2352,13 +2352,13 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28" s="3" t="b">
         <v>0</v>
@@ -2370,32 +2370,32 @@
         <v>0</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="3" t="b">
         <v>1</v>
@@ -2407,32 +2407,32 @@
         <v>0</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="3" t="b">
         <v>1</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="4">
@@ -2461,13 +2461,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="3" t="b">
         <v>1</v>
@@ -2479,10 +2479,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
@@ -2491,18 +2491,18 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32" s="3" t="b">
         <v>0</v>
@@ -2514,34 +2514,34 @@
         <v>0</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" s="3" t="b">
         <v>0</v>
@@ -2553,32 +2553,32 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
       <c r="K33" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" s="3" t="b">
         <v>0</v>
@@ -2590,34 +2590,34 @@
         <v>0</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" s="3" t="b">
         <v>0</v>
@@ -2629,34 +2629,34 @@
         <v>0</v>
       </c>
       <c r="G35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
       <c r="K35" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="C36" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" s="3" t="b">
         <v>0</v>
@@ -2668,34 +2668,34 @@
         <v>0</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
       <c r="K36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" s="3" t="b">
         <v>0</v>
@@ -2707,34 +2707,34 @@
         <v>0</v>
       </c>
       <c r="G37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
       <c r="K37" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O37" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D38" s="3" t="b">
         <v>0</v>
@@ -2746,34 +2746,34 @@
         <v>0</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="4">
         <v>108</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" s="3" t="b">
         <v>0</v>
@@ -2785,34 +2785,34 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
       <c r="K39" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" s="3" t="b">
         <v>0</v>
@@ -2824,34 +2824,34 @@
         <v>0</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
       <c r="K40" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="C41" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="3" t="b">
         <v>1</v>
@@ -2863,34 +2863,34 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="4">
         <v>66</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42" s="3" t="b">
         <v>0</v>
@@ -2902,34 +2902,34 @@
         <v>0</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" s="3" t="b">
         <v>0</v>
@@ -2941,34 +2941,34 @@
         <v>0</v>
       </c>
       <c r="G43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
       <c r="K43" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O43" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" s="3" t="b">
         <v>1</v>
@@ -2980,14 +2980,14 @@
         <v>0</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
@@ -2997,13 +2997,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" s="3" t="b">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
@@ -3026,19 +3026,19 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" s="3" t="b">
         <v>1</v>
@@ -3050,14 +3050,14 @@
         <v>0</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -3067,32 +3067,32 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="H47" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -3102,13 +3102,13 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48" s="3" t="b">
         <v>0</v>
@@ -3120,10 +3120,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="4">
@@ -3133,19 +3133,19 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D49" s="3" t="b">
         <v>1</v>
@@ -3157,32 +3157,32 @@
         <v>0</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" s="3" t="b">
         <v>0</v>
@@ -3194,34 +3194,34 @@
         <v>0</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51" s="3" t="b">
         <v>1</v>
@@ -3233,10 +3233,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
@@ -3248,13 +3248,13 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" s="3" t="b">
         <v>0</v>
@@ -3266,34 +3266,34 @@
         <v>0</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="4">
         <v>15</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" s="3" t="b">
         <v>0</v>
@@ -3305,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="4">
@@ -3318,19 +3318,19 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D54" s="3" t="b">
         <v>0</v>
@@ -3342,34 +3342,34 @@
         <v>0</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" s="3" t="b">
         <v>0</v>
@@ -3381,34 +3381,34 @@
         <v>0</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D56" s="3" t="b">
         <v>0</v>
@@ -3420,73 +3420,73 @@
         <v>0</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="4"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="H57" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D58" s="3" t="b">
         <v>0</v>
@@ -3498,34 +3498,34 @@
         <v>0</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D59" s="3" t="b">
         <v>0</v>
@@ -3537,36 +3537,36 @@
         <v>0</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O59" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D60" s="3" t="b">
         <v>0</v>
@@ -3578,32 +3578,32 @@
         <v>0</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C61" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" s="3" t="b">
         <v>0</v>
@@ -3615,73 +3615,73 @@
         <v>0</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="4"/>
       <c r="K61" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>201</v>
-      </c>
       <c r="H62" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="4">
         <v>40</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" s="3" t="b">
         <v>1</v>
@@ -3693,34 +3693,34 @@
         <v>0</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O63" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D64" s="3" t="b">
         <v>1</v>
@@ -3732,14 +3732,14 @@
         <v>0</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I64" s="3"/>
       <c r="J64" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
@@ -3749,13 +3749,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="C65" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D65" s="3" t="b">
         <v>0</v>
@@ -3767,34 +3767,34 @@
         <v>0</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="4">
         <v>111</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D66" s="3" t="b">
         <v>1</v>
@@ -3806,34 +3806,34 @@
         <v>0</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O66" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="C67" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D67" s="3" t="b">
         <v>0</v>
@@ -3845,34 +3845,34 @@
         <v>0</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="C68" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D68" s="3" t="b">
         <v>1</v>
@@ -3884,14 +3884,14 @@
         <v>0</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
@@ -3901,13 +3901,13 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D69" s="3" t="b">
         <v>1</v>
@@ -3919,10 +3919,10 @@
         <v>0</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="4">
@@ -3932,19 +3932,19 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D70" s="3" t="b">
         <v>0</v>
@@ -3956,34 +3956,34 @@
         <v>0</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D71" s="3" t="b">
         <v>1</v>
@@ -3995,32 +3995,32 @@
         <v>0</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
       <c r="O71" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" s="3" t="b">
         <v>0</v>
@@ -4032,34 +4032,34 @@
         <v>0</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="4"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D73" s="3" t="b">
         <v>1</v>
@@ -4071,14 +4071,14 @@
         <v>0</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
@@ -4088,13 +4088,13 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D74" s="3" t="b">
         <v>0</v>
@@ -4106,36 +4106,36 @@
         <v>0</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="C75" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D75" s="3" t="b">
         <v>1</v>
@@ -4147,14 +4147,14 @@
         <v>0</v>
       </c>
       <c r="G75" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
@@ -4164,13 +4164,13 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="C76" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D76" s="3" t="b">
         <v>0</v>
@@ -4182,10 +4182,10 @@
         <v>0</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="4"/>
@@ -4193,19 +4193,19 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
       <c r="N76" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C77" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D77" s="3" t="b">
         <v>0</v>
@@ -4217,32 +4217,32 @@
         <v>0</v>
       </c>
       <c r="G77" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="4"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D78" s="3" t="b">
         <v>1</v>
@@ -4254,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="4">
@@ -4271,13 +4271,13 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D79" s="3" t="b">
         <v>1</v>
@@ -4289,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="4"/>
@@ -4301,18 +4301,18 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="C80" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D80" s="3" t="b">
         <v>0</v>
@@ -4324,34 +4324,34 @@
         <v>0</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="4">
         <v>159</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="C81" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D81" s="3" t="b">
         <v>1</v>
@@ -4363,32 +4363,32 @@
         <v>0</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D82" s="3" t="b">
         <v>0</v>
@@ -4400,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="4">
@@ -4413,19 +4413,19 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D83" s="3" t="b">
         <v>0</v>
@@ -4437,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="4">
@@ -4450,19 +4450,19 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="C84" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D84" s="3" t="b">
         <v>0</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="4">
@@ -4487,19 +4487,19 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D85" s="3" t="b">
         <v>0</v>
@@ -4511,10 +4511,10 @@
         <v>0</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I85" s="3"/>
       <c r="J85" s="4">
@@ -4524,19 +4524,19 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="C86" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D86" s="3" t="b">
         <v>1</v>
@@ -4548,14 +4548,14 @@
         <v>0</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I86" s="3"/>
       <c r="J86" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
@@ -4565,14 +4565,14 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="D87" s="3" t="b">
         <v>1</v>
       </c>
@@ -4583,10 +4583,10 @@
         <v>0</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I87" s="3"/>
       <c r="J87" s="4">
@@ -4600,28 +4600,28 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D88" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>268</v>
-      </c>
       <c r="H88" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="4">
@@ -4631,21 +4631,21 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="O88" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="C89" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D89" s="3" t="b">
         <v>1</v>
@@ -4657,10 +4657,10 @@
         <v>0</v>
       </c>
       <c r="G89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="4">
@@ -4674,13 +4674,13 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="C90" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D90" s="3" t="b">
         <v>1</v>
@@ -4692,14 +4692,14 @@
         <v>0</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I90" s="3"/>
       <c r="J90" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
@@ -4709,13 +4709,13 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D91" s="3" t="b">
         <v>0</v>
@@ -4727,34 +4727,34 @@
         <v>0</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I91" s="3"/>
       <c r="J91" s="4">
         <v>111</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="C92" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D92" s="3" t="b">
         <v>0</v>
@@ -4766,36 +4766,36 @@
         <v>0</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I92" s="3"/>
       <c r="J92" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
       <c r="M92" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D93" s="3" t="b">
         <v>0</v>
@@ -4807,32 +4807,32 @@
         <v>0</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="4"/>
       <c r="K93" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
       <c r="N93" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="C94" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D94" s="3" t="b">
         <v>0</v>
@@ -4844,34 +4844,34 @@
         <v>0</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I94" s="3"/>
       <c r="J94" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O94" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D95" s="3" t="b">
         <v>1</v>
@@ -4883,32 +4883,32 @@
         <v>0</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I95" s="3"/>
       <c r="J95" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D96" s="3" t="b">
         <v>1</v>
@@ -4920,32 +4920,32 @@
         <v>0</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
       <c r="O96" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="C97" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D97" s="3" t="b">
         <v>1</v>
@@ -4957,32 +4957,32 @@
         <v>0</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I97" s="3"/>
       <c r="J97" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
       <c r="O97" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="C98" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D98" s="3" t="b">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I98" s="3"/>
       <c r="J98" s="4">
@@ -5007,21 +5007,21 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
       <c r="N98" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="O98" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="C99" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D99" s="3" t="b">
         <v>0</v>
@@ -5033,10 +5033,10 @@
         <v>0</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I99" s="3"/>
       <c r="J99" s="4">
@@ -5046,21 +5046,21 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
       <c r="N99" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="O99" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="C100" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D100" s="3" t="b">
         <v>0</v>
@@ -5072,10 +5072,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I100" s="3"/>
       <c r="J100" s="4">
@@ -5085,21 +5085,21 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
       <c r="N100" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="O100" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="C101" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D101" s="3" t="b">
         <v>0</v>
@@ -5111,10 +5111,10 @@
         <v>0</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I101" s="3"/>
       <c r="J101" s="4">
@@ -5124,10 +5124,10 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
       <c r="N101" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/SWTest/Outputs/Finalists/Navigator_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/Navigator_Analysis_Final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA2D7F3-C6B0-4ADC-8039-646C0A96EA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04818789-08FC-4D2D-9096-2D950DE824E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18900" yWindow="3516" windowWidth="16416" windowHeight="8856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1318,24 +1318,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="175" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>100</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>103</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>106</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>110</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>112</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>130</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>135</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>143</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>149</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>152</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>156</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>159</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>163</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>165</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>167</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>169</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>172</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>176</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>179</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>189</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>194</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>201</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>205</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>207</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>210</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>213</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>215</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>219</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>221</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>224</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>226</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>229</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>231</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>234</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>238</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>240</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>243</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>246</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>246</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>250</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>252</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>254</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>257</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>259</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>262</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>264</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>266</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>269</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>276</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>278</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>281</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>284</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>287</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>292</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>295</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>297</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>299</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>303</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>305</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>307</v>
       </c>
